--- a/data/trans_camb/IP26C_R-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>2.272481767862236</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.399263228282518</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.248532911970344</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.708762733337932</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.232613674437001</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>5.343650700097065</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-1.350401704754694</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.482335977542607</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.594119599871226</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.112600411719407</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.390254721953866</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.330222837840725</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>6.064843408992417</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.12787594129849</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.805848430115287</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>15.85356674691812</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>5.18292903654859</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.1077267531665</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.3882546573841713</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.5807658387934971</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.2826851498356486</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.9691442525569036</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3245046131795032</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.7766857845832434</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.1763707199129075</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.242339821305087</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.1717899543930879</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.09523880843828356</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.05805607307614775</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.1556616496098952</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>1.551247071759457</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2.190224236553328</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1.148768480800201</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2.459833667068221</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.9220691643719775</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.753821785758608</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-2.577584031216027</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-5.655652428708509</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.048120914976146</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-4.28760310021875</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-2.812248450754072</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-4.916140402022361</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-8.392246092098848</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.41541067637045</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.951481723143611</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.092501505874099</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-6.41907250716611</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-8.557040354275239</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.187465141464429</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.02589736726659198</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.691844607770431</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.8590656643169464</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.067906791145452</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-1.112344763666473</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.1657541921138043</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.3636925461377857</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.2508708753233832</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3528845386369939</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2030064900796573</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3548791741660486</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.451781549854156</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.60663988602215</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.5334300036916177</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.636022455354149</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3975407872905384</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5462083233620614</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.2513126631338543</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.01638884876010279</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.204035164272257</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.1105963172061844</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.09992201945092055</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.07313813810042201</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-4.161638868309184</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.400709227544048</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9539704898380894</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-3.142683956458737</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-1.617149225994462</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-2.051538572569134</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-9.809599880811696</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.874521615113532</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.251676491492224</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.285043075726055</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-5.736160489042392</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-5.892059237112949</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>2.032196190147771</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.64668289472983</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.294161905395543</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.676993629631118</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.281560584585299</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.519212047829434</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.3157725871909896</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.1062815853754218</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.09696260680572487</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.3194258439131453</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.1401399890826808</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1777835888866335</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.6024612317379587</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.4370673724156518</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.3533105941850314</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.6422849251780914</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.4198241968848604</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4373769486061907</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.2423255719829855</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.4913573673097891</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1.152866066917352</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.3068903273644171</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2383655159327517</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.1658576944336198</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-1.534828791184439</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4.476320053071232</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-3.390737108528323</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.452075382283749</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-2.36527642378911</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>3.042805458503249</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-8.122027786258021</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.268724248697325</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-10.6630586405884</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-6.323128722198717</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-6.932687465823471</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.478712606912052</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>3.899024447025122</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>11.0202067518143</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.193072912086921</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>8.518862921200329</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>2.339167291197787</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>7.548919104381238</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.1928631520046856</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.5624843629307152</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.363696561941302</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.1557522176779486</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2758563369564871</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.3548748718804082</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.7210500866677794</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.254065815609665</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.7864460730550621</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.4557957582843133</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.6416295599276967</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.1417302867438922</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.9055606267869194</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2.370930153114396</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.9112565650258381</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1.56511930256886</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.4519408521852141</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.217013135509556</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.28312458263041</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.3227643975964409</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.3217795166388038</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.5806123232948074</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.8147242054465889</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.08448622690775814</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.78178887824778</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-2.62622666559195</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.974531385768803</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-3.236027717523719</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.80880930953834</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-2.18597079746932</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.191515533718481</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.244367813251628</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>2.566570516993107</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2.330632351184718</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.899776951494877</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.908749222125378</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.1203890064791598</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.0302833299895342</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.03265611973929899</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.0589240289428085</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.07936396865545588</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.008229977972054523</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.3162371851094938</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.2196348938123227</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2640951484991477</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.2839393250780966</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.2446156114952736</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.1939809808599224</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.1315291289783963</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.3400216432934048</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.301070636952291</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.2755432910245819</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.09800015508856709</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.2052388640277326</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
